--- a/aq_files/0407.xlsx
+++ b/aq_files/0407.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -46,13 +45,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -135,44 +136,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -199,14 +200,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -233,6 +252,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -244,166 +281,142 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
@@ -413,377 +426,658 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TOPIC:</t>
+          <t>Question No.</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>NoSQL Intro</t>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>What is Data Preparation for Ranking Analysis?</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Foundations</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DATASET (MongoDB)</t>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Why is Data Preparation for Ranking Analysis important in Data Preparation for Ranking Analysis?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Importance</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>use companyDB</t>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Explain the main workflow of Data Preparation for Ranking Analysis.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Process Understanding</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>db.employees.insertMany([... full realistic employee docs ...])</t>
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>List the key components involved in Data Preparation for Ranking Analysis.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Component Awareness</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>db.departments.insertMany([...])</t>
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>How is Data Preparation for Ranking Analysis applied in a practical business scenario?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Applied Understanding</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>db.projects.insertMany([...])</t>
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>What problem does Data Preparation for Ranking Analysis help solve?</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Problem Framing</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>db.assignments.insertMany([...])</t>
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Describe the core steps required to complete Data Preparation for Ranking Analysis.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Execution Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What inputs are typically required before starting Data Preparation for Ranking Analysis?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Input Readiness</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Q.No</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What outputs or results are expected from Data Preparation for Ranking Analysis?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Output Interpretation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A startup is building a social media platform with dynamic user profiles. Should they use SQL or Document DB? Justify your choice.</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>How would you validate whether Data Preparation for Ranking Analysis was completed correctly?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Validation</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>An e-commerce system stores structured orders but flexible product attributes. Decide between SQL and MongoDB.</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>What are common mistakes to avoid while working on Data Preparation for Ranking Analysis?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Error Awareness</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A system stores deeply nested JSON logs. Explain why Document DB is suitable.</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>How does Data Preparation for Ranking Analysis improve decision-making or outcomes?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Business Value</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A banking system requires strict ACID properties. Should SQL or NoSQL be used?</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>What assumptions should be checked before using Data Preparation for Ranking Analysis?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Assumption Checking</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>An IoT platform generates large-scale flexible data. Which DB is suitable and why?</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>How would you explain Data Preparation for Ranking Analysis to a beginner?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Concept Simplification</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A company wants to avoid JOIN operations for performance. How does Document DB help?</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>What metrics or indicators are useful when evaluating Data Preparation for Ranking Analysis?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Measurement</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Explain how schema-less design benefits agile development.</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>How does Data Preparation for Ranking Analysis connect with earlier modules in the course?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Module Integration</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A system requires horizontal scaling. Why is MongoDB preferred?</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>What are the prerequisites for learning Data Preparation for Ranking Analysis?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Compare normalization vs denormalization.</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Compare Data Preparation for Ranking Analysis with a simpler alternative approach.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Comparison</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Explain Document DB for storing nested user profiles.</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>When should Data Preparation for Ranking Analysis not be used?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Limitations</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Ranking Analysis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A reporting system needs heavy joins. Why SQL is better?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Explain BSON format in MongoDB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Frequent schema changes cause issues in SQL. How does NoSQL solve this?</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>14</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Explain flexibility vs consistency trade-offs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>15</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Why microservices prefer Document DB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Compare indexing in SQL vs MongoDB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>17</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Explain hierarchical data handling in Document DB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>18</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Explain transaction limitations in MongoDB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>19</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Explain CAP theorem in MongoDB context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>20</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Design database choice for ride-sharing app and justify.</t>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Summarize the most important learning point from Data Preparation for Ranking Analysis.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/RANKING ANALYSIS/Data Preparation for Ranking Analysis</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Retention</t>
         </is>
       </c>
     </row>
